--- a/Payment_Gateway_Test_Cases.xlsx
+++ b/Payment_Gateway_Test_Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="170">
   <si>
     <t>Payment Gateway Sandbox Testing – Test Case Template</t>
   </si>
@@ -576,6 +576,15 @@
   </si>
   <si>
     <t>OTP verification screen appeared during card payment flow, requesting OTP for card ending 5449</t>
+  </si>
+  <si>
+    <t>System correctly rejected invalid</t>
+  </si>
+  <si>
+    <t>Attempted manual double-click testing; browser/UI timing made it difficult</t>
+  </si>
+  <si>
+    <t>Not Executed</t>
   </si>
 </sst>
 </file>
@@ -663,7 +672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -684,6 +693,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1451,8 +1463,12 @@
       <c r="G12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="H12" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="J12" s="5" t="s">
         <v>34</v>
       </c>
@@ -1552,8 +1568,12 @@
       <c r="G15" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>169</v>
+      </c>
       <c r="J15" s="5" t="s">
         <v>34</v>
       </c>

--- a/Payment_Gateway_Test_Cases.xlsx
+++ b/Payment_Gateway_Test_Cases.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="179">
   <si>
     <t>Payment Gateway Sandbox Testing – Test Case Template</t>
   </si>
@@ -585,6 +585,33 @@
   </si>
   <si>
     <t>Not Executed</t>
+  </si>
+  <si>
+    <t>Clicked browser Back button while payment was processing (after card details submitted, before OTP screen fully loaded).Dashboard confirmed final status as "Customer – Payment Cancelled" — a specific, clear status label distinguishing user-initiated cancellation from other failure types like timeout or decline.</t>
+  </si>
+  <si>
+    <t>Issued a partial refund (₹74 out of ₹100 captured amount) via Razorpay Dashboard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triggered "International cards not supported" restriction on this test merchant account — consistent with the pattern observed across multiple card numbers throughout this project </t>
+  </si>
+  <si>
+    <t>Triggered "International cards not supported" restriction on this test merchant account — consistent with the pattern observed across multiple card numbers throughout this project</t>
+  </si>
+  <si>
+    <t>International cards not supported</t>
+  </si>
+  <si>
+    <t>Entered past expiry date (01/20). System correctly blocked submission with inline error "Please enter a valid expiry date." No API call triggered.</t>
+  </si>
+  <si>
+    <t>Left CVV field blank. System correctly blocked with inline error "Please enter a 3 digit cvv.</t>
+  </si>
+  <si>
+    <t>Verified transaction details in dashboard matched checkout confirmation exactly (amount, status, card). Observed full lifecycle timeline: Created → Authorized → Captured → Settlement scheduled.</t>
+  </si>
+  <si>
+    <t>Issued full refund (₹100) on captured transaction. Refund ID generated, Normal speed, 3-5 day processing confirmed via dashboard timeline.</t>
   </si>
 </sst>
 </file>
@@ -645,7 +672,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -668,11 +695,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -696,6 +734,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1070,9 +1111,9 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
@@ -1172,8 +1213,12 @@
       <c r="G3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="H3" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>163</v>
+      </c>
       <c r="J3" s="5" t="s">
         <v>34</v>
       </c>
@@ -1203,8 +1248,12 @@
       <c r="G4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>169</v>
+      </c>
       <c r="J4" s="5" t="s">
         <v>43</v>
       </c>
@@ -1234,8 +1283,12 @@
       <c r="G5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="H5" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>169</v>
+      </c>
       <c r="J5" s="5" t="s">
         <v>43</v>
       </c>
@@ -1300,8 +1353,12 @@
       <c r="G7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="H7" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>163</v>
+      </c>
       <c r="J7" s="5" t="s">
         <v>34</v>
       </c>
@@ -1397,8 +1454,12 @@
       <c r="G10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="H10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>169</v>
+      </c>
       <c r="J10" s="5" t="s">
         <v>43</v>
       </c>
@@ -1603,8 +1664,12 @@
       <c r="G16" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="H16" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="J16" s="5" t="s">
         <v>43</v>
       </c>
@@ -1634,8 +1699,12 @@
       <c r="G17" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="H17" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="J17" s="5" t="s">
         <v>43</v>
       </c>
@@ -1665,8 +1734,12 @@
       <c r="G18" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="H18" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="J18" s="5" t="s">
         <v>34</v>
       </c>
@@ -1696,8 +1769,12 @@
       <c r="G19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="J19" s="5" t="s">
         <v>34</v>
       </c>
@@ -1727,8 +1804,12 @@
       <c r="G20" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+      <c r="H20" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="J20" s="5" t="s">
         <v>34</v>
       </c>
@@ -1758,8 +1839,12 @@
       <c r="G21" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="J21" s="5" t="s">
         <v>43</v>
       </c>
@@ -1769,7 +1854,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="I2:I21">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I21 H10">
       <formula1>"Pass,Fail,Blocked,Not Executed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
